--- a/excel/output_stats_sfvv/2mm/PerSubgraphStats.xlsx
+++ b/excel/output_stats_sfvv/2mm/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,10 +1481,10 @@
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>343.684</v>
+        <v>338.925</v>
       </c>
       <c r="O22" t="n">
-        <v>345.65</v>
+        <v>340.89</v>
       </c>
     </row>
     <row r="23">
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>343.684</v>
+        <v>338.925</v>
       </c>
       <c r="O23" t="n">
-        <v>352.13</v>
+        <v>345.27</v>
       </c>
     </row>
     <row r="24">
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>0.653234</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3.69673</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.176706</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2.41483</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>750439000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2774170000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2575810000</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>11090200000</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>3000000000</v>
@@ -1578,7 +1578,7 @@
         <v>343.01</v>
       </c>
       <c r="O24" t="n">
-        <v>352.1</v>
+        <v>345.04</v>
       </c>
     </row>
     <row r="25">
@@ -1586,34 +1586,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
-        <v>1.20329e-09</v>
+        <v>0.653234</v>
       </c>
       <c r="D25" t="n">
-        <v>5e-09</v>
+        <v>3.69673</v>
       </c>
       <c r="E25" t="n">
-        <v>0.240657</v>
+        <v>0.176706</v>
       </c>
       <c r="F25" t="n">
-        <v>6.016420000000001e-18</v>
+        <v>2.41483</v>
       </c>
       <c r="G25" t="n">
-        <v>600000000</v>
+        <v>750439000</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>2774170000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2575810000</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>11090200000</v>
       </c>
       <c r="L25" t="n">
         <v>3000000000</v>
@@ -1622,10 +1622,10 @@
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>350.151</v>
+        <v>343.01</v>
       </c>
       <c r="O25" t="n">
-        <v>350.19</v>
+        <v>352.1</v>
       </c>
     </row>
     <row r="26">
@@ -1633,35 +1633,35 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>8.646599999999999e-09</v>
+        <v>1.20329e-09</v>
       </c>
       <c r="D26" t="n">
-        <v>3.33333e-08</v>
+        <v>5e-09</v>
       </c>
       <c r="E26" t="n">
-        <v>0.259398</v>
+        <v>0.240657</v>
       </c>
       <c r="F26" t="n">
-        <v>2.8822e-16</v>
+        <v>6.016420000000001e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>870000000</v>
+        <v>600000000</v>
       </c>
       <c r="H26" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>15</v>
       </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
       <c r="L26" t="n">
         <v>3000000000</v>
       </c>
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O26" t="n">
-        <v>350.17</v>
+        <v>350.19</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>4.76522e-10</v>
+        <v>8.646599999999999e-09</v>
       </c>
       <c r="D27" t="n">
-        <v>2e-09</v>
+        <v>3.33333e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>0.238261</v>
+        <v>0.259398</v>
       </c>
       <c r="F27" t="n">
-        <v>9.530439999999999e-19</v>
+        <v>2.8822e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>500000000</v>
+        <v>870000000</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="L27" t="n">
         <v>3000000000</v>
@@ -1727,7 +1727,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
         <v>4.76522e-10</v>
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>6.24265e-10</v>
+        <v>4.76522e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>2.33333e-09</v>
+        <v>2e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>0.267542</v>
+        <v>0.238261</v>
       </c>
       <c r="F29" t="n">
-        <v>1.45662e-18</v>
+        <v>9.530439999999999e-19</v>
       </c>
       <c r="G29" t="n">
-        <v>857143000</v>
+        <v>500000000</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
         <v>3000000000</v>
@@ -1810,7 +1810,7 @@
         <v>0.6</v>
       </c>
       <c r="N29" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O29" t="n">
         <v>350.17</v>
@@ -1821,7 +1821,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
         <v>6.24265e-10</v>
@@ -1868,34 +1868,34 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>1.48585e-09</v>
+        <v>6.24265e-10</v>
       </c>
       <c r="D31" t="n">
-        <v>5.66667e-09</v>
+        <v>2.33333e-09</v>
       </c>
       <c r="E31" t="n">
-        <v>0.262208</v>
+        <v>0.267542</v>
       </c>
       <c r="F31" t="n">
-        <v>8.419790000000001e-18</v>
+        <v>1.45662e-18</v>
       </c>
       <c r="G31" t="n">
-        <v>705882000</v>
+        <v>857143000</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
         <v>3000000000</v>
@@ -1904,7 +1904,7 @@
         <v>0.6</v>
       </c>
       <c r="N31" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O31" t="n">
         <v>350.17</v>
@@ -1915,45 +1915,92 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.48585e-09</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5.66667e-09</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.262208</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8.419790000000001e-18</v>
+      </c>
+      <c r="G32" t="n">
+        <v>705882000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>350.17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C32" t="n">
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="n">
         <v>1.21265e-10</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D33" t="n">
         <v>3.33333e-10</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>0.363794</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>4.04216e-20</v>
       </c>
-      <c r="G32" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="G33" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="H33" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>3000000000</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="L33" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N33" t="n">
         <v>350.151</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>350.22</v>
       </c>
     </row>
